--- a/Kolkata-January-2026.xlsx
+++ b/Kolkata-January-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Kolkata</t>
   </si>
   <si>
@@ -115,13 +118,13 @@
     <t>WB04J4973</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>EC3</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>15/03/2023</t>
@@ -492,10 +495,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,25 +577,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>122</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2">
         <v>44206</v>
@@ -655,27 +661,27 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>123</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3">
         <v>115934</v>
@@ -735,27 +741,27 @@
         <v>52.08</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4">
         <v>74717</v>
@@ -815,24 +821,24 @@
         <v>31.35</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="2">
         <v>45357</v>
@@ -895,27 +901,27 @@
         <v>44.05</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6">
         <v>45246</v>
